--- a/从零开始学Slots/从零开始学Slots-37-基础篇-SuperStack与MysterySymbols.xlsx
+++ b/从零开始学Slots/从零开始学Slots-37-基础篇-SuperStack与MysterySymbols.xlsx
@@ -4129,6 +4129,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:L121" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -4713,5 +4716,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M60" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-37-基础篇-SuperStack与MysterySymbols.xlsx
+++ b/从零开始学Slots/从零开始学Slots-37-基础篇-SuperStack与MysterySymbols.xlsx
@@ -3109,9 +3109,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00%"/>
+    <numFmt numFmtId="166" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -3289,7 +3290,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3408,6 +3409,10 @@
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" applyNumberFormat="1" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -4456,7 +4461,7 @@
       <c r="E24" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="F24" s="20" t="n">
+      <c r="F24" s="30" t="n">
         <f aca="false">SUM(B24:E24)</f>
         <v>1</v>
       </c>
@@ -4478,7 +4483,7 @@
       <c r="E25" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="F25" s="20" t="n">
+      <c r="F25" s="30" t="n">
         <f aca="false">SUM(B25:E25)</f>
         <v>1</v>
       </c>
@@ -4500,7 +4505,7 @@
       <c r="E26" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="F26" s="20" t="n">
+      <c r="F26" s="30" t="n">
         <f aca="false">SUM(B26:E26)</f>
         <v>1</v>
       </c>
@@ -4522,7 +4527,7 @@
       <c r="E27" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="F27" s="20" t="n">
+      <c r="F27" s="30" t="n">
         <f aca="false">SUM(B27:E27)</f>
         <v>1</v>
       </c>
@@ -4544,7 +4549,7 @@
       <c r="E28" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="F28" s="20" t="n">
+      <c r="F28" s="30" t="n">
         <f aca="false">SUM(B28:E28)</f>
         <v>1</v>
       </c>
@@ -4599,7 +4604,7 @@
       <c r="E32" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="F32" s="20" t="n">
+      <c r="F32" s="30" t="n">
         <f aca="false">SUM(B32:E32)</f>
         <v>1</v>
       </c>
